--- a/data/trans_orig/P70D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de su capacidad laboral actual en 2023</t>
+          <t>Población según su autopercepción de su capacidad laboral actual en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -728,12 +728,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90864</t>
+          <t>90530</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128849</t>
+          <t>125896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66177</t>
+          <t>65211</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90911</t>
+          <t>90069</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163620</t>
+          <t>165313</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207889</t>
+          <t>208620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71130</t>
+          <t>71944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103392</t>
+          <t>104994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51409</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74280</t>
+          <t>74905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129926</t>
+          <t>130242</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172349</t>
+          <t>170336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79640</t>
+          <t>77867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118019</t>
+          <t>115071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68885</t>
+          <t>69894</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95275</t>
+          <t>96192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>156576</t>
+          <t>157422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200827</t>
+          <t>202031</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34878</t>
+          <t>36909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23737</t>
+          <t>23330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27973</t>
+          <t>26922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53305</t>
+          <t>51474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>20041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15952</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30530</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13434</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1616,97 +1616,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3925</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1090</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>3740</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1090</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1873,62 +1873,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1199</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>889</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3688</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84713</t>
+          <t>76250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>283254</t>
+          <t>286173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80999</t>
+          <t>80900</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112166</t>
+          <t>109574</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133527</t>
+          <t>151687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>365061</t>
+          <t>366008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213715</t>
+          <t>210733</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>623857</t>
+          <t>630422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101012</t>
+          <t>103127</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135682</t>
+          <t>136168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334480</t>
+          <t>330635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>884415</t>
+          <t>852709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68577</t>
+          <t>70201</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>240915</t>
+          <t>240192</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>119570</t>
+          <t>119597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>152757</t>
+          <t>155564</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>140467</t>
+          <t>148477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>380444</t>
+          <t>383850</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58350</t>
+          <t>60502</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37653</t>
+          <t>37001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29371</t>
+          <t>32075</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88201</t>
+          <t>90774</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>20109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>781</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -2954,97 +2954,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2915</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>1404</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5310</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>5024</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -3065,97 +3065,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2915</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3738</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>842</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3417</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4229</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4307</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>764</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>126455</t>
+          <t>125090</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>167751</t>
+          <t>167702</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>121746</t>
+          <t>119852</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>204576</t>
+          <t>204676</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>260015</t>
+          <t>258549</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>352198</t>
+          <t>358085</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>52,53%</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80967</t>
+          <t>79633</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>118415</t>
+          <t>117833</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47202</t>
+          <t>45346</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83755</t>
+          <t>82916</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>138285</t>
+          <t>135580</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>190715</t>
+          <t>192992</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57903</t>
+          <t>55779</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>94455</t>
+          <t>91197</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>50979</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94961</t>
+          <t>94856</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>123976</t>
+          <t>125493</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>176247</t>
+          <t>178494</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16177</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>40450</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35176</t>
+          <t>35498</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>37073</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>66670</t>
+          <t>67036</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3898,47 +3898,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>9466</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>4806</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>16552</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>2,43%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>9466</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>4857</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>17761</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -4181,97 +4181,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>2066</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4292,97 +4292,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>2066</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4438,47 +4438,47 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>880</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4549,62 +4549,62 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>7032</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>7903</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>150735</t>
+          <t>151159</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>193456</t>
+          <t>197391</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>89609</t>
+          <t>86186</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>173476</t>
+          <t>172000</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>240998</t>
+          <t>235142</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>354083</t>
+          <t>353531</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>99969</t>
+          <t>100149</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>138505</t>
+          <t>141898</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>110454</t>
+          <t>111355</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>284761</t>
+          <t>295031</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>227203</t>
+          <t>229385</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>441569</t>
+          <t>450420</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>107445</t>
+          <t>107149</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>147806</t>
+          <t>147171</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>65059</t>
+          <t>64544</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>133100</t>
+          <t>133463</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>183690</t>
+          <t>179436</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>265382</t>
+          <t>264598</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>39288</t>
+          <t>41544</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>40400</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>39825</t>
+          <t>38344</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>71066</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>12482</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>32079</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>19262</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>45332</t>
+          <t>46023</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>40363</t>
+          <t>35679</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>479</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5741,97 +5741,97 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>1889</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3654</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="S49" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>2984</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>3601</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>3434</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -5852,97 +5852,97 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>1889</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>1689</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>429231</t>
+          <t>374173</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>720694</t>
+          <t>723172</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>396944</t>
+          <t>401919</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>538004</t>
+          <t>533742</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>846002</t>
+          <t>829683</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1199173</t>
+          <t>1195316</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>516881</t>
+          <t>513755</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1101042</t>
+          <t>1214383</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>348449</t>
+          <t>352638</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>582346</t>
+          <t>574774</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>905732</t>
+          <t>909197</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1687297</t>
+          <t>1656796</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,29%</t>
         </is>
       </c>
     </row>
@@ -6302,12 +6302,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>301033</t>
+          <t>265738</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>530830</t>
+          <t>533171</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>341864</t>
+          <t>348749</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>443784</t>
+          <t>447533</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>663246</t>
+          <t>676970</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>959748</t>
+          <t>955252</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>71303</t>
+          <t>70868</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>139277</t>
+          <t>141579</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>78721</t>
+          <t>79634</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>115829</t>
+          <t>117285</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>162013</t>
+          <t>158828</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>245015</t>
+          <t>244146</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>31528</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>64796</t>
+          <t>67635</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6539,49 +6539,49 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>35983</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>26655</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>48219</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
           <t>3,29%</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>35983</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>25995</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>48662</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>106</t>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>64067</t>
+          <t>63569</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>106637</t>
+          <t>108241</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6635,12 +6635,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>22892</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>50331</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>60842</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18776</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -6857,12 +6857,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -6968,12 +6968,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Habitat-trans_orig.xlsx
@@ -723,32 +723,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>108496</t>
+          <t>118636</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90530</t>
+          <t>99388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125896</t>
+          <t>138931</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -758,32 +758,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>77758</t>
+          <t>84339</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65211</t>
+          <t>69899</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90069</t>
+          <t>97208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>186254</t>
+          <t>202975</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165313</t>
+          <t>179719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208620</t>
+          <t>227337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -834,32 +834,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87817</t>
+          <t>98960</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71944</t>
+          <t>81377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104994</t>
+          <t>118853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62313</t>
+          <t>65463</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>53036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74905</t>
+          <t>78916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>150130</t>
+          <t>164423</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130242</t>
+          <t>143843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170336</t>
+          <t>188403</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -945,32 +945,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96007</t>
+          <t>105544</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77867</t>
+          <t>85907</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115071</t>
+          <t>124547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -980,32 +980,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>82366</t>
+          <t>91309</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69894</t>
+          <t>77398</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96192</t>
+          <t>105510</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1015,32 +1015,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>178372</t>
+          <t>196853</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>157422</t>
+          <t>174934</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>202031</t>
+          <t>222842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21385</t>
+          <t>22563</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36909</t>
+          <t>39848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23330</t>
+          <t>25429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>38219</t>
+          <t>40337</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51474</t>
+          <t>57148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1237,32 +1237,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>22567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>33913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1313,32 +1313,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1348,22 +1348,22 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1459,17 +1459,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>895</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>556</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1792,22 +1792,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>903</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>903</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1946,17 +1946,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>331095</t>
+          <t>364541</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>331095</t>
+          <t>364541</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>331095</t>
+          <t>364541</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>256678</t>
+          <t>277407</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>256678</t>
+          <t>277407</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>256678</t>
+          <t>277407</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>587773</t>
+          <t>641947</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>587773</t>
+          <t>641947</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>587773</t>
+          <t>641947</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2061,32 +2061,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>188308</t>
+          <t>207234</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76250</t>
+          <t>180358</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>286173</t>
+          <t>236946</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>94936</t>
+          <t>105895</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80900</t>
+          <t>90637</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109574</t>
+          <t>123910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2131,32 +2131,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>283243</t>
+          <t>313129</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151687</t>
+          <t>281673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366008</t>
+          <t>342802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -2172,32 +2172,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>401515</t>
+          <t>175137</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210733</t>
+          <t>149219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>630422</t>
+          <t>202568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2207,32 +2207,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>117285</t>
+          <t>128865</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103127</t>
+          <t>111307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136168</t>
+          <t>145635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>518800</t>
+          <t>304002</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>330635</t>
+          <t>274105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>852709</t>
+          <t>333709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -2283,32 +2283,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>159343</t>
+          <t>178038</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70201</t>
+          <t>152061</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>240192</t>
+          <t>202825</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2318,32 +2318,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>136311</t>
+          <t>153885</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>119597</t>
+          <t>133930</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155564</t>
+          <t>172738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2353,32 +2353,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>295654</t>
+          <t>331924</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>148477</t>
+          <t>300889</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>383850</t>
+          <t>364144</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -2394,32 +2394,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>44662</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>30158</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60502</t>
+          <t>63869</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2429,32 +2429,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28206</t>
+          <t>33115</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37001</t>
+          <t>43323</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2464,32 +2464,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>64021</t>
+          <t>77776</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>61765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90774</t>
+          <t>97617</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -2505,32 +2505,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20109</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2540,32 +2540,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2575,32 +2575,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>25823</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35485</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2616,32 +2616,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2651,32 +2651,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>13216</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2686,32 +2686,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>21086</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2762,32 +2762,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2797,32 +2797,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2873,32 +2873,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2908,32 +2908,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>845</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>845</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3241,32 +3241,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3284,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>806317</t>
+          <t>628535</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>806317</t>
+          <t>628535</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>806317</t>
+          <t>628535</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>402160</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>402160</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>402160</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1208477</t>
+          <t>1078384</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1208477</t>
+          <t>1078384</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1208477</t>
+          <t>1078384</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3399,32 +3399,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>146916</t>
+          <t>179593</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>125090</t>
+          <t>155170</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>167702</t>
+          <t>204280</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>146611</t>
+          <t>132230</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>119852</t>
+          <t>115061</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>204676</t>
+          <t>148704</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>293526</t>
+          <t>311823</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>258549</t>
+          <t>280324</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>358085</t>
+          <t>339125</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -3510,32 +3510,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>99230</t>
+          <t>113621</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>79633</t>
+          <t>94133</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>117833</t>
+          <t>137878</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3545,32 +3545,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>67691</t>
+          <t>78231</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>64110</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82916</t>
+          <t>92256</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3580,32 +3580,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>166921</t>
+          <t>191852</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>135580</t>
+          <t>168080</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>192992</t>
+          <t>217571</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -3621,32 +3621,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>73911</t>
+          <t>85305</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55779</t>
+          <t>66776</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>91197</t>
+          <t>106325</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3656,32 +3656,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>78572</t>
+          <t>93499</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>79714</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94856</t>
+          <t>108821</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3691,32 +3691,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>152482</t>
+          <t>178804</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>125493</t>
+          <t>156764</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>178494</t>
+          <t>204069</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -3732,32 +3732,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>20580</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40450</t>
+          <t>46591</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3767,17 +3767,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>24505</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35498</t>
+          <t>37198</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3802,32 +3802,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>50343</t>
+          <t>57094</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>37073</t>
+          <t>42234</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>73881</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -3843,32 +3843,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>12421</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3878,32 +3878,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3913,32 +3913,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3989,32 +3989,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4024,22 +4024,22 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>11477</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>693</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>870</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>870</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4589,12 +4589,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4622,17 +4622,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4657,17 +4657,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>324345</t>
+          <t>338934</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>324345</t>
+          <t>338934</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>324345</t>
+          <t>338934</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>681713</t>
+          <t>760531</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>681713</t>
+          <t>760531</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>681713</t>
+          <t>760531</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4737,32 +4737,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>173715</t>
+          <t>191083</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>151159</t>
+          <t>168506</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>197391</t>
+          <t>216070</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4772,32 +4772,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>141817</t>
+          <t>155065</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>86186</t>
+          <t>137366</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>172000</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4807,32 +4807,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>315533</t>
+          <t>346149</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>235142</t>
+          <t>319019</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>353531</t>
+          <t>379372</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>119023</t>
+          <t>127455</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>100149</t>
+          <t>106796</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>141898</t>
+          <t>148616</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>168788</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>111355</t>
+          <t>92925</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>295031</t>
+          <t>126213</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>287811</t>
+          <t>235938</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>229385</t>
+          <t>210537</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>450420</t>
+          <t>263313</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -4959,32 +4959,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>125740</t>
+          <t>134341</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>107149</t>
+          <t>112751</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>147171</t>
+          <t>156156</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4994,32 +4994,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>107762</t>
+          <t>120871</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>64544</t>
+          <t>103415</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>133463</t>
+          <t>137341</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5029,32 +5029,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>233503</t>
+          <t>255212</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>179436</t>
+          <t>229482</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>264598</t>
+          <t>281290</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -5070,32 +5070,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>41544</t>
+          <t>51150</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>40400</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5140,32 +5140,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>55131</t>
+          <t>66181</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>52863</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>71066</t>
+          <t>84855</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -5181,32 +5181,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>20267</t>
+          <t>21866</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>35905</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5216,32 +5216,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>20852</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5251,32 +5251,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>31892</t>
+          <t>35149</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>46023</t>
+          <t>50244</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>22214</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5362,22 +5362,22 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>17896</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>38871</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -5403,102 +5403,102 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4916</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>4683</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>9661</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>1766</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>5173</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>4672</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>1778</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>11032</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5549,32 +5549,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5584,32 +5584,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -5660,27 +5660,27 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5695,17 +5695,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>648</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>648</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -5960,17 +5960,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5995,17 +5995,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>480460</t>
+          <t>448507</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>480460</t>
+          <t>448507</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>480460</t>
+          <t>448507</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6030,17 +6030,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>952663</t>
+          <t>966368</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>952663</t>
+          <t>966368</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>952663</t>
+          <t>966368</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6075,32 +6075,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>617434</t>
+          <t>696546</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>374173</t>
+          <t>649340</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>723172</t>
+          <t>745352</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6110,32 +6110,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>461122</t>
+          <t>477530</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>401919</t>
+          <t>445435</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>533742</t>
+          <t>512618</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1078556</t>
+          <t>1174076</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>829683</t>
+          <t>1115583</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1195316</t>
+          <t>1234637</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -6186,32 +6186,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>707585</t>
+          <t>515172</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>513755</t>
+          <t>474516</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1214383</t>
+          <t>558838</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6221,32 +6221,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>416076</t>
+          <t>381042</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>352638</t>
+          <t>352488</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>574774</t>
+          <t>409963</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6256,32 +6256,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>1123662</t>
+          <t>896215</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>909197</t>
+          <t>843995</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1656796</t>
+          <t>954988</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -6297,32 +6297,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>455001</t>
+          <t>503228</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>265738</t>
+          <t>462067</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>533171</t>
+          <t>552410</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6332,32 +6332,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>405010</t>
+          <t>459564</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>348749</t>
+          <t>428191</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>447533</t>
+          <t>495089</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6367,32 +6367,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>860011</t>
+          <t>962792</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>676970</t>
+          <t>907123</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>955252</t>
+          <t>1015872</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -6408,32 +6408,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>110058</t>
+          <t>134548</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>70868</t>
+          <t>111472</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>141579</t>
+          <t>164383</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6443,32 +6443,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>97655</t>
+          <t>106840</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>79634</t>
+          <t>89216</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>117285</t>
+          <t>126154</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6478,32 +6478,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>207713</t>
+          <t>241388</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>158828</t>
+          <t>212052</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>244146</t>
+          <t>271739</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -6519,32 +6519,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>30587</t>
+          <t>40569</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>67635</t>
+          <t>72150</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6554,32 +6554,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>35983</t>
+          <t>40854</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>48219</t>
+          <t>54106</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6589,32 +6589,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>84909</t>
+          <t>94702</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>63569</t>
+          <t>76141</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>108241</t>
+          <t>117486</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -6630,32 +6630,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6665,32 +6665,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>40572</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6700,32 +6700,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>60842</t>
+          <t>56342</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -6741,32 +6741,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6776,67 +6776,67 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>11452</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>6422</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>18737</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>11053</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>6456</t>
-        </is>
-      </c>
-      <c r="T58" s="2" t="inlineStr">
-        <is>
-          <t>18776</t>
-        </is>
-      </c>
-      <c r="U58" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -6852,32 +6852,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6887,67 +6887,67 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>17599</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>9163</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>15830</t>
-        </is>
-      </c>
-      <c r="U59" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -6998,17 +6998,17 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7018,39 +7018,39 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>5076</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2475</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>9927</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>5041</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>2264</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>9151</t>
-        </is>
-      </c>
-      <c r="U60" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -7074,17 +7074,17 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7109,17 +7109,17 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7144,17 +7144,17 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -7185,32 +7185,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7255,17 +7255,17 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7333,17 +7333,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
